--- a/docs/AMSON-Test-Plan.xlsx
+++ b/docs/AMSON-Test-Plan.xlsx
@@ -2808,7 +2808,7 @@
     <t xml:space="preserve">Compare 'Active Online Orders' with the Online Orders page.</t>
   </si>
   <si>
-    <t xml:space="preserve">Counts only open orders (not delivered/received/closed). Known issue REQ047 - note result.</t>
+    <t xml:space="preserve">Counts only payment-confirmed and dispatched orders (not pending, delivered, received or closed), on load and as orders change.</t>
   </si>
   <si>
     <t xml:space="preserve">T11-03</t>
@@ -3345,7 +3345,7 @@
     <t xml:space="preserve">Resubmitted order returns to the queue; approve it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Old hold cleared; Payment Confirmed; customer notified (check REQ098 bug).</t>
+    <t xml:space="preserve">Old hold cleared (no On Hold badge in Online Orders); Payment Confirmed; customer gets the confirmation notice and email.</t>
   </si>
   <si>
     <t xml:space="preserve">T13-20</t>
@@ -14429,7 +14429,7 @@
       <c r="J177" s="10"/>
       <c r="K177" s="7"/>
     </row>
-    <row r="178" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
         <v>924</v>
       </c>
